--- a/results/exp01-svhn-vgg11-e8-ours/20260921-202952/rounds.xlsx
+++ b/results/exp01-svhn-vgg11-e8-ours/20260921-202952/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7341,6 +7341,1500 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:54:15</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.5811361665960333</v>
+      </c>
+      <c r="F84" t="n">
+        <v>94.93315918869084</v>
+      </c>
+      <c r="G84" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="H84" t="n">
+        <v>81</v>
+      </c>
+      <c r="I84" t="n">
+        <v>58.3181</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0:58.32</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>55.8253</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1334</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.3587</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5063.1517</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:24:23.15</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:51;4:10;2:41;7:37;5:10;0:10;6:53;1:63;8:39;3:42</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[0,2,3,4,7];4:[0];2:[0,2,3,7];7:[0,2,3];5:[3];0:[0];6:[0,2,3,4,6];1:[0,1,2,3,4,7];8:[0,3,7];3:[0,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=51,experts=[0,2,3,4,7]; c4:bw=10,experts=[0]; c2:bw=41,experts=[0,2,3,7]; c7:bw=37,experts=[0,2,3]; c5:bw=10,experts=[3]; c0:bw=10,experts=[0]; c6:bw=53,experts=[0,2,3,4,6]; c1:bw=63,experts=[0,1,2,3,4,7]; c8:bw=39,experts=[0,3,7]; c3:bw=42,experts=[0,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2.8818,6.5867,7.2223,11.2560,2.1368,3.7841,8.4082,9.9235,2.4337,1.1922</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:55:14</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.5789397483981333</v>
+      </c>
+      <c r="F85" t="n">
+        <v>94.89090350338046</v>
+      </c>
+      <c r="G85" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="H85" t="n">
+        <v>81</v>
+      </c>
+      <c r="I85" t="n">
+        <v>58.7034</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0:58.70</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>56.0982</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.4634</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5121.8875</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:25:21.89</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:67;3:32;1:58;6:10;9:20;2:36;7:47;5:20;4:27;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[0,1,2,3,4,7];3:[0,3,5];1:[0,1,2,3,7];6:[0];9:[0,3];2:[0,3,7];7:[0,3,5,6];5:[0,3];4:[0,3];0:[0]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=67,experts=[0,1,2,3,4,7]; c3:bw=32,experts=[0,3,5]; c1:bw=58,experts=[0,1,2,3,7]; c6:bw=10,experts=[0]; c9:bw=20,experts=[0,3]; c2:bw=36,experts=[0,3,7]; c7:bw=47,experts=[0,3,5,6]; c5:bw=20,experts=[0,3]; c4:bw=27,experts=[0,3]; c0:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2.4854,1.1944,10.0321,8.4410,2.8488,7.2754,11.2719,2.1563,6.5882,3.8047</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:56:12</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.580214335195113</v>
+      </c>
+      <c r="F86" t="n">
+        <v>94.97541487400123</v>
+      </c>
+      <c r="G86" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="H86" t="n">
+        <v>81</v>
+      </c>
+      <c r="I86" t="n">
+        <v>58.2389</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0:58.24</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>55.7184</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.3842</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5180.2273</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:26:20.23</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:38;2:45;8:70;6:42;1:57;4:42;9:58;3:51;5:12;7:11</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[0,2,5];2:[0,3,4,7];8:[0,1,2,3,4,6,7];6:[0,3,4,7];1:[0,2,3,4,7];4:[0,3,6,7];9:[0,1,3,4,6];3:[0,1,3,4,5];5:[5];7:[3]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[0,2,5]; c2:bw=45,experts=[0,3,4,7]; c8:bw=70,experts=[0,1,2,3,4,6,7]; c6:bw=42,experts=[0,3,4,7]; c1:bw=57,experts=[0,2,3,4,7]; c4:bw=42,experts=[0,3,6,7]; c9:bw=58,experts=[0,1,3,4,6]; c3:bw=51,experts=[0,1,3,4,5]; c5:bw=12,experts=[5]; c7:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>3.8155,7.2084,2.4569,8.4078,9.9615,6.5477,2.8252,1.1943,2.1087,11.1924</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:57:11</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.5803981965286873</v>
+      </c>
+      <c r="F87" t="n">
+        <v>95.0560848186847</v>
+      </c>
+      <c r="G87" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="H87" t="n">
+        <v>81</v>
+      </c>
+      <c r="I87" t="n">
+        <v>58.5062</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0:58.51</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>55.9301</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5238.9731</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:27:18.97</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:47;8:28;2:24;6:55;0:30;4:18;7:44;3:28;1:72;9:43</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[0,3,4,7];8:[0,3];2:[0,3];6:[0,1,3,4,7];0:[0,3,7];4:[0];7:[0,2,3,7];3:[0,3];1:[0,1,2,3,4,6,7];9:[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[0,3,4,7]; c8:bw=28,experts=[0,3]; c2:bw=24,experts=[0,3]; c6:bw=55,experts=[0,1,3,4,7]; c0:bw=30,experts=[0,3,7]; c4:bw=18,experts=[0]; c7:bw=44,experts=[0,2,3,7]; c3:bw=28,experts=[0,3]; c1:bw=72,experts=[0,1,2,3,4,6,7]; c9:bw=43,experts=[0,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2.1759,2.4561,7.2522,8.4368,3.8309,6.6195,11.2520,1.1912,9.9045,2.8108</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:58:10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5790530822366113</v>
+      </c>
+      <c r="F88" t="n">
+        <v>95.14059618930547</v>
+      </c>
+      <c r="G88" t="n">
+        <v>95.21358328211431</v>
+      </c>
+      <c r="H88" t="n">
+        <v>81</v>
+      </c>
+      <c r="I88" t="n">
+        <v>58.6451</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0:58.65</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>56.1065</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.4041</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5297.6491</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:28:17.65</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:29;2:67;7:22;5:10;6:60;3:68;4:34;9:37;8:46;0:35</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[0,3];2:[0,1,3,4,6,7];7:[0,3];5:[1];6:[0,2,3,4,5,7];3:[0,2,3,5,6,7];4:[1,2,4];9:[0,3,4];8:[0,2,3,7];0:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=29,experts=[0,3]; c2:bw=67,experts=[0,1,3,4,6,7]; c7:bw=22,experts=[0,3]; c5:bw=10,experts=[1]; c6:bw=60,experts=[0,2,3,4,5,7]; c3:bw=68,experts=[0,2,3,5,6,7]; c4:bw=34,experts=[1,2,4]; c9:bw=37,experts=[0,3,4]; c8:bw=46,experts=[0,2,3,7]; c0:bw=35,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>10.0392,7.2717,11.2979,2.1291,8.4444,1.2132,6.5555,2.8546,2.4634,3.8376</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:59:08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.5770572377783086</v>
+      </c>
+      <c r="F89" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="G89" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H89" t="n">
+        <v>88</v>
+      </c>
+      <c r="I89" t="n">
+        <v>58.6174</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0:58.62</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>56.0691</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.4159</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5356.2994</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:29:16.30</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:43;6:27;3:33;7:41;0:62;4:38;9:31;1:28;5:30;2:46</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[0,3,5,7];6:[0,3];3:[0,3,4];7:[0,1,3,7];0:[0,1,2,3,6,7];4:[0,3,7];9:[0,3,5];1:[0,3];5:[2,3,6];2:[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=43,experts=[0,3,5,7]; c6:bw=27,experts=[0,3]; c3:bw=33,experts=[0,3,4]; c7:bw=41,experts=[0,1,3,7]; c0:bw=62,experts=[0,1,2,3,6,7]; c4:bw=38,experts=[0,3,7]; c9:bw=31,experts=[0,3,5]; c1:bw=28,experts=[0,3]; c5:bw=30,experts=[2,3,6]; c2:bw=46,experts=[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2.4672,8.5001,1.2359,11.3190,3.8449,6.6224,2.8283,9.9899,2.1088,7.1526</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:00:07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5773134214201454</v>
+      </c>
+      <c r="F90" t="n">
+        <v>95.06376767055932</v>
+      </c>
+      <c r="G90" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H90" t="n">
+        <v>88</v>
+      </c>
+      <c r="I90" t="n">
+        <v>58.2666</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0:58.27</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>55.7527</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.3688</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5414.5981</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:30:14.60</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:31;8:74;2:44;9:60;7:21;5:46;0:13;6:32;4:30;1:41</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[0,3,5];8:[0,1,2,3,4,5,7];2:[0,3,4,7];9:[0,1,3,4,5,6];7:[3,4];5:[0,2,3,7];0:[4];6:[0,3,4];4:[0,3,5];1:[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=31,experts=[0,3,5]; c8:bw=74,experts=[0,1,2,3,4,5,7]; c2:bw=44,experts=[0,3,4,7]; c9:bw=60,experts=[0,1,3,4,5,6]; c7:bw=21,experts=[3,4]; c5:bw=46,experts=[0,2,3,7]; c0:bw=13,experts=[4]; c6:bw=32,experts=[0,3,4]; c4:bw=30,experts=[0,3,5]; c1:bw=41,experts=[0,3,5,7]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>1.1806,2.4474,7.2158,2.8344,11.2066,2.1386,3.7622,8.3969,6.5750,9.9953</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:01:05</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5754922125037637</v>
+      </c>
+      <c r="F91" t="n">
+        <v>95.07913337430854</v>
+      </c>
+      <c r="G91" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H91" t="n">
+        <v>88</v>
+      </c>
+      <c r="I91" t="n">
+        <v>58.6576</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0:58.66</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>56.1071</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.4108</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5473.2887</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:31:13.29</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:72;1:31;3:36;9:63;0:64;6:26;2:21;5:27;8:50;4:35</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,5,6,7];1:[0,3,7];3:[0,3,5];9:[0,1,3,4,5,6];0:[0,2,3,5,6,7];6:[0,3];2:[0,3];5:[0,3];8:[0,1,3,4,7];4:[0,3,7]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=72,experts=[0,2,3,4,5,6,7]; c1:bw=31,experts=[0,3,7]; c3:bw=36,experts=[0,3,5]; c9:bw=63,experts=[0,1,3,4,5,6]; c0:bw=64,experts=[0,2,3,5,6,7]; c6:bw=26,experts=[0,3]; c2:bw=21,experts=[0,3]; c5:bw=27,experts=[0,3]; c8:bw=50,experts=[0,1,3,4,7]; c4:bw=35,experts=[0,3,7]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>11.3831,10.0423,1.2083,2.8712,3.8584,8.4514,7.1673,2.1454,2.4321,6.5476</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:02:04</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.5767933863600427</v>
+      </c>
+      <c r="F92" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="G92" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H92" t="n">
+        <v>88</v>
+      </c>
+      <c r="I92" t="n">
+        <v>58.2595</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0:58.26</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>55.7088</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.4075</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5531.5802</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:32:11.58</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:50;9:35;5:52;7:51;3:40;4:54;0:22;6:29;2:11;8:23</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[0,2,3,4,7];9:[0,2,3];5:[0,2,3,4,7];7:[0,2,3,6,7];3:[0,3,5,7];4:[0,3,5,6,7];0:[0,3];6:[3,6];2:[2];8:[0,3]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[0,2,3,4,7]; c9:bw=35,experts=[0,2,3]; c5:bw=52,experts=[0,2,3,4,7]; c7:bw=51,experts=[0,2,3,6,7]; c3:bw=40,experts=[0,3,5,7]; c4:bw=54,experts=[0,3,5,6,7]; c0:bw=22,experts=[0,3]; c6:bw=29,experts=[3,6]; c2:bw=11,experts=[2]; c8:bw=23,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>9.9908,2.8612,2.1348,11.2096,1.1966,6.5818,3.8027,8.3324,7.1600,2.4388</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:03:02</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.5784726464757429</v>
+      </c>
+      <c r="F93" t="n">
+        <v>95.06760909649662</v>
+      </c>
+      <c r="G93" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H93" t="n">
+        <v>88</v>
+      </c>
+      <c r="I93" t="n">
+        <v>58.5453</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0:58.55</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>55.9661</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2.4483</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5590.1596</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:33:10.16</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:28;7:34;1:20;0:29;8:19;6:45;9:56;2:25;5:66;4:26</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[0,3];7:[0,3,7];1:[0,3];0:[0,3];8:[3];6:[0,3,4,5];9:[0,1,3,4,6];2:[0,3];5:[0,2,3,4,6,7];4:[0,3]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=28,experts=[0,3]; c7:bw=34,experts=[0,3,7]; c1:bw=20,experts=[0,3]; c0:bw=29,experts=[0,3]; c8:bw=19,experts=[3]; c6:bw=45,experts=[0,3,4,5]; c9:bw=56,experts=[0,1,3,4,6]; c2:bw=25,experts=[0,3]; c5:bw=66,experts=[0,2,3,4,6,7]; c4:bw=26,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1.2112,11.3346,10.0654,3.8121,2.4642,8.4288,2.8302,7.1732,2.1279,6.5185</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:04:01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5761708988619345</v>
+      </c>
+      <c r="F94" t="n">
+        <v>95.31730178242164</v>
+      </c>
+      <c r="G94" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H94" t="n">
+        <v>88</v>
+      </c>
+      <c r="I94" t="n">
+        <v>58.2833</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0:58.28</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>55.7767</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.3719</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5648.4752</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:34:08.48</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:47;3:31;7:22;9:58;6:22;8:10;5:10;4:32;0:19;2:51</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[0,2,3,4];3:[0,1,3];7:[0,3];9:[0,3,4,5,6];6:[0,3];8:[6];5:[5];4:[0,3,7];0:[0];2:[0,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=47,experts=[0,2,3,4]; c3:bw=31,experts=[0,1,3]; c7:bw=22,experts=[0,3]; c9:bw=58,experts=[0,3,4,5,6]; c6:bw=22,experts=[0,3]; c8:bw=10,experts=[6]; c5:bw=10,experts=[5]; c4:bw=32,experts=[0,3,7]; c0:bw=19,experts=[0]; c2:bw=51,experts=[0,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>9.9410,1.2020,11.2714,2.8421,8.3784,2.4211,2.1133,6.6294,3.8034,7.1746</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:04:59</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.5769238010125587</v>
+      </c>
+      <c r="F95" t="n">
+        <v>95.22894898586355</v>
+      </c>
+      <c r="G95" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H95" t="n">
+        <v>88</v>
+      </c>
+      <c r="I95" t="n">
+        <v>58.6875</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0:58.69</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>56.1462</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.4009</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5707.1969</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:35:07.20</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:45;2:65;5:41;4:31;6:30;9:50;1:70;8:10;0:55;3:34</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,7];2:[0,2,3,4,6,7];5:[0,2,3,4];4:[0,3,7];6:[0,1,3];9:[0,3,4,6,7];1:[0,1,2,3,5,6,7];8:[3];0:[0,2,3,6,7];3:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=45,experts=[0,2,3,7]; c2:bw=65,experts=[0,2,3,4,6,7]; c5:bw=41,experts=[0,2,3,4]; c4:bw=31,experts=[0,3,7]; c6:bw=30,experts=[0,1,3]; c9:bw=50,experts=[0,3,4,6,7]; c1:bw=70,experts=[0,1,2,3,5,6,7]; c8:bw=10,experts=[3]; c0:bw=55,experts=[0,2,3,6,7]; c3:bw=34,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>11.3982,7.3113,2.1629,6.6458,8.4437,2.8513,9.9370,2.4314,3.7766,1.1880</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:05:58</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.5764251076099121</v>
+      </c>
+      <c r="F96" t="n">
+        <v>95.06376767055932</v>
+      </c>
+      <c r="G96" t="n">
+        <v>95.37108174554395</v>
+      </c>
+      <c r="H96" t="n">
+        <v>88</v>
+      </c>
+      <c r="I96" t="n">
+        <v>58.6417</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0:58.64</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>55.9938</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.419</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5765.8722</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:36:05.87</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:59;9:42;4:15;6:40;0:35;3:41;1:31;8:76;2:23;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[0,2,3,4,7];9:[0,3,4,6];4:[1];6:[0,2,3,7];0:[0,3,6];3:[0,2,3,6];1:[0,3,7];8:[0,1,2,3,4,5,7];2:[1,3];5:[1]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=59,experts=[0,2,3,4,7]; c9:bw=42,experts=[0,3,4,6]; c4:bw=15,experts=[1]; c6:bw=40,experts=[0,2,3,7]; c0:bw=35,experts=[0,3,6]; c3:bw=41,experts=[0,2,3,6]; c1:bw=31,experts=[0,3,7]; c8:bw=76,experts=[0,1,2,3,4,5,7]; c2:bw=23,experts=[1,3]; c5:bw=10,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>11.3426,2.8518,6.6061,8.4303,3.8161,1.1967,10.0015,2.4603,7.1763,2.1120</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:06:56</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5757409312656709</v>
+      </c>
+      <c r="F97" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="G97" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>58.411</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0:58.41</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>55.9084</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.3711</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5824.3178</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:37:04.32</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:65;9:44;3:46;1:36;5:60;4:49;6:31;7:50;0:36;8:64</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,3,4,5,6,7];9:[0,3,4,6];3:[0,1,3,5];1:[0,3,7];5:[0,1,2,3,4,7];4:[0,2,3,4];6:[0,3,4];7:[0,1,2,3,7];0:[0,1,3];8:[0,1,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=65,experts=[0,3,4,5,6,7]; c9:bw=44,experts=[0,3,4,6]; c3:bw=46,experts=[0,1,3,5]; c1:bw=36,experts=[0,3,7]; c5:bw=60,experts=[0,1,2,3,4,7]; c4:bw=49,experts=[0,2,3,4]; c6:bw=31,experts=[0,3,4]; c7:bw=50,experts=[0,1,2,3,7]; c0:bw=36,experts=[0,1,3]; c8:bw=64,experts=[0,1,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>7.2797,2.8641,1.2027,10.0128,2.1433,6.6186,8.4019,11.1532,3.8120,2.4201</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:07:55</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5742114713651547</v>
+      </c>
+      <c r="F98" t="n">
+        <v>95.09065765212047</v>
+      </c>
+      <c r="G98" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="H98" t="n">
+        <v>96</v>
+      </c>
+      <c r="I98" t="n">
+        <v>58.2466</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0:58.25</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>55.745</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.3654</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5882.5978</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:38:02.60</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:41;9:43;8:43;4:16;7:30;1:50;3:35;5:46;6:50;2:54</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[0,3,4,7];9:[0,3,6,7];8:[0,2,3,5];4:[0];7:[0,3,7];1:[0,1,2,3,4];3:[0,3,7];5:[0,2,3,7];6:[0,3,4,6,7];2:[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=41,experts=[0,3,4,7]; c9:bw=43,experts=[0,3,6,7]; c8:bw=43,experts=[0,2,3,5]; c4:bw=16,experts=[0]; c7:bw=30,experts=[0,3,7]; c1:bw=50,experts=[0,1,2,3,4]; c3:bw=35,experts=[0,3,7]; c5:bw=46,experts=[0,2,3,7]; c6:bw=50,experts=[0,3,4,6,7]; c2:bw=54,experts=[0,2,3,4,7]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>3.8520,2.8386,2.4481,6.5562,11.2395,9.9609,1.1948,2.1417,8.3744,7.1387</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:08:53</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.5740271348548497</v>
+      </c>
+      <c r="F99" t="n">
+        <v>95.19437615242778</v>
+      </c>
+      <c r="G99" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="H99" t="n">
+        <v>96</v>
+      </c>
+      <c r="I99" t="n">
+        <v>58.3708</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0:58.37</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>55.8758</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.3638</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5941.0045</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:39:01.00</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:52;8:54;9:27;7:24;6:36;5:49;0:33;3:25;1:26;2:24</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[0,3,5,6,7];8:[0,1,3,5,7];9:[0,3];7:[3,5];6:[0,3,4];5:[0,3,4,7];0:[0,3,5];3:[0,3];1:[0,3];2:[0,3]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=52,experts=[0,3,5,6,7]; c8:bw=54,experts=[0,1,3,5,7]; c9:bw=27,experts=[0,3]; c7:bw=24,experts=[3,5]; c6:bw=36,experts=[0,3,4]; c5:bw=49,experts=[0,3,4,7]; c0:bw=33,experts=[0,3,5]; c3:bw=25,experts=[0,3]; c1:bw=26,experts=[0,3]; c2:bw=24,experts=[0,3]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>6.6308,2.4728,2.8635,11.2930,8.4266,2.1441,3.8115,1.2069,9.8985,7.1281</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:09:52</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.5754501968602412</v>
+      </c>
+      <c r="F100" t="n">
+        <v>95.23663183773817</v>
+      </c>
+      <c r="G100" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="H100" t="n">
+        <v>96</v>
+      </c>
+      <c r="I100" t="n">
+        <v>58.3825</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0:58.38</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>55.8395</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.4018</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5999.4216</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:39:59.42</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:34;5:49;7:45;1:59;3:38;9:20;4:24;0:40;2:31;6:35</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[0,3,7];5:[0,3,4,7];7:[0,3,6,7];1:[0,1,2,3,4];3:[0,3,4];9:[2,3];4:[0,3];0:[0,2,3,7];2:[0,3,4];6:[0,3,4]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=34,experts=[0,3,7]; c5:bw=49,experts=[0,3,4,7]; c7:bw=45,experts=[0,3,6,7]; c1:bw=59,experts=[0,1,2,3,4]; c3:bw=38,experts=[0,3,4]; c9:bw=20,experts=[2,3]; c4:bw=24,experts=[0,3]; c0:bw=40,experts=[0,2,3,7]; c2:bw=31,experts=[0,3,4]; c6:bw=35,experts=[0,3,4]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>2.4682,2.1375,11.2621,9.9630,1.1837,2.9009,6.5850,3.8112,7.1501,8.3778</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:50</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5736414548088884</v>
+      </c>
+      <c r="F101" t="n">
+        <v>95.2980946527351</v>
+      </c>
+      <c r="G101" t="n">
+        <v>95.3979717271051</v>
+      </c>
+      <c r="H101" t="n">
+        <v>96</v>
+      </c>
+      <c r="I101" t="n">
+        <v>58.5161</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0:58.52</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>56.0341</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.3513</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6057.9739</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:40:57.97</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:30;8:44;9:53;5:18;6:44;1:17;4:65;7:10;3:42;0:64</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[0,3,7];8:[0,3,4,7];9:[0,1,3,4,6];5:[6];6:[0,3,4,5];1:[3];4:[0,2,3,5,6,7];7:[3];3:[0,3,4,5];0:[0,2,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[0,3,7]; c8:bw=44,experts=[0,3,4,7]; c9:bw=53,experts=[0,1,3,4,6]; c5:bw=18,experts=[6]; c6:bw=44,experts=[0,3,4,5]; c1:bw=17,experts=[3]; c4:bw=65,experts=[0,2,3,5,6,7]; c7:bw=10,experts=[3]; c3:bw=42,experts=[0,3,4,5]; c0:bw=64,experts=[0,2,3,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>7.2918,2.4899,2.8716,2.1315,8.4548,9.9595,6.5718,11.2557,1.1939,3.8135</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
